--- a/artfynd/A 32279-2024 artfynd.xlsx
+++ b/artfynd/A 32279-2024 artfynd.xlsx
@@ -2841,10 +2841,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119660128</v>
+        <v>119660132</v>
       </c>
       <c r="B20" t="n">
-        <v>74577</v>
+        <v>79569</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2853,25 +2853,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
+        <v>515</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pectenia plumbea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>293901</v>
+        <v>293858</v>
       </c>
       <c r="R20" t="n">
-        <v>6548493</v>
+        <v>6548464</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2930,17 +2930,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119660132</v>
+        <v>119660128</v>
       </c>
       <c r="B21" t="n">
-        <v>79569</v>
+        <v>74577</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2970,25 +2970,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>515</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pectenia plumbea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lightf.) P.M.Jørg. et al.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>293858</v>
+        <v>293901</v>
       </c>
       <c r="R21" t="n">
-        <v>6548464</v>
+        <v>6548493</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3047,17 +3047,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 32279-2024 artfynd.xlsx
+++ b/artfynd/A 32279-2024 artfynd.xlsx
@@ -2958,10 +2958,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119660128</v>
+        <v>119660135</v>
       </c>
       <c r="B21" t="n">
-        <v>74577</v>
+        <v>94410</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>2667</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>293901</v>
+        <v>293876</v>
       </c>
       <c r="R21" t="n">
-        <v>6548493</v>
+        <v>6548504</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3047,17 +3047,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119660134</v>
+        <v>119660133</v>
       </c>
       <c r="B22" t="n">
-        <v>90334</v>
+        <v>79567</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3091,21 +3091,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3215</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>293867</v>
+        <v>293859</v>
       </c>
       <c r="R22" t="n">
-        <v>6548479</v>
+        <v>6548466</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3161,6 +3161,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3177,10 +3192,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119660120</v>
+        <v>119660110</v>
       </c>
       <c r="B23" t="n">
-        <v>90971</v>
+        <v>91494</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3193,21 +3208,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5321</v>
+        <v>4769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3217,10 +3232,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>293865</v>
+        <v>293855</v>
       </c>
       <c r="R23" t="n">
-        <v>6548470</v>
+        <v>6548516</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3261,7 +3276,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3397,10 +3411,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119660123</v>
+        <v>119660120</v>
       </c>
       <c r="B25" t="n">
-        <v>74577</v>
+        <v>90971</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3413,21 +3427,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>5321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Rigidoporus corticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3437,10 +3451,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>294010</v>
+        <v>293865</v>
       </c>
       <c r="R25" t="n">
-        <v>6548481</v>
+        <v>6548470</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3481,6 +3495,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3499,10 +3514,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119660125</v>
+        <v>119660131</v>
       </c>
       <c r="B26" t="n">
-        <v>90573</v>
+        <v>74577</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3515,21 +3530,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1205</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3539,10 +3554,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>294011</v>
+        <v>293850</v>
       </c>
       <c r="R26" t="n">
-        <v>6548504</v>
+        <v>6548486</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3616,7 +3631,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119660131</v>
+        <v>119660126</v>
       </c>
       <c r="B27" t="n">
         <v>74577</v>
@@ -3656,10 +3671,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>293850</v>
+        <v>293933</v>
       </c>
       <c r="R27" t="n">
-        <v>6548486</v>
+        <v>6548488</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3705,17 +3720,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3733,10 +3748,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119660110</v>
+        <v>119660137</v>
       </c>
       <c r="B28" t="n">
-        <v>91494</v>
+        <v>94410</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3749,21 +3764,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>2667</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3773,10 +3788,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>293855</v>
+        <v>293882</v>
       </c>
       <c r="R28" t="n">
-        <v>6548516</v>
+        <v>6548507</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3819,6 +3834,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3835,10 +3865,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119660133</v>
+        <v>119660134</v>
       </c>
       <c r="B29" t="n">
-        <v>79567</v>
+        <v>90334</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3851,21 +3881,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>3215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3875,10 +3905,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>293859</v>
+        <v>293867</v>
       </c>
       <c r="R29" t="n">
-        <v>6548466</v>
+        <v>6548479</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3921,21 +3951,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3952,10 +3967,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119660135</v>
+        <v>119660128</v>
       </c>
       <c r="B30" t="n">
-        <v>94410</v>
+        <v>74577</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3968,21 +3983,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2667</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3992,10 +4007,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>293876</v>
+        <v>293901</v>
       </c>
       <c r="R30" t="n">
-        <v>6548504</v>
+        <v>6548493</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4041,17 +4056,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4069,10 +4084,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119660126</v>
+        <v>119660125</v>
       </c>
       <c r="B31" t="n">
-        <v>74577</v>
+        <v>90573</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4085,21 +4100,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6426</v>
+        <v>1205</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4109,10 +4124,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>293933</v>
+        <v>294011</v>
       </c>
       <c r="R31" t="n">
-        <v>6548488</v>
+        <v>6548504</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4158,17 +4173,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4186,10 +4201,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119660137</v>
+        <v>119660123</v>
       </c>
       <c r="B32" t="n">
-        <v>94410</v>
+        <v>74577</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4202,21 +4217,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2667</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4226,10 +4241,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>293882</v>
+        <v>294010</v>
       </c>
       <c r="R32" t="n">
-        <v>6548507</v>
+        <v>6548481</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4272,21 +4287,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">

--- a/artfynd/A 32279-2024 artfynd.xlsx
+++ b/artfynd/A 32279-2024 artfynd.xlsx
@@ -3075,10 +3075,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119660133</v>
+        <v>119660110</v>
       </c>
       <c r="B22" t="n">
-        <v>79567</v>
+        <v>91494</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3091,21 +3091,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>293859</v>
+        <v>293855</v>
       </c>
       <c r="R22" t="n">
-        <v>6548466</v>
+        <v>6548516</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3161,21 +3161,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3192,10 +3177,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119660110</v>
+        <v>119660133</v>
       </c>
       <c r="B23" t="n">
-        <v>91494</v>
+        <v>79567</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3208,21 +3193,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4769</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3232,10 +3217,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>293855</v>
+        <v>293859</v>
       </c>
       <c r="R23" t="n">
-        <v>6548516</v>
+        <v>6548466</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3278,6 +3263,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3865,10 +3865,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119660134</v>
+        <v>119660128</v>
       </c>
       <c r="B29" t="n">
-        <v>90334</v>
+        <v>74577</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>293867</v>
+        <v>293901</v>
       </c>
       <c r="R29" t="n">
-        <v>6548479</v>
+        <v>6548493</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3951,6 +3951,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3967,10 +3982,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119660128</v>
+        <v>119660134</v>
       </c>
       <c r="B30" t="n">
-        <v>74577</v>
+        <v>90334</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3983,21 +3998,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>3215</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4007,10 +4022,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>293901</v>
+        <v>293867</v>
       </c>
       <c r="R30" t="n">
-        <v>6548493</v>
+        <v>6548479</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4053,21 +4068,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">

--- a/artfynd/A 32279-2024 artfynd.xlsx
+++ b/artfynd/A 32279-2024 artfynd.xlsx
@@ -2841,10 +2841,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119660132</v>
+        <v>119660125</v>
       </c>
       <c r="B20" t="n">
-        <v>79569</v>
+        <v>90573</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2853,25 +2853,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>515</v>
+        <v>1205</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blylav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pectenia plumbea</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lightf.) P.M.Jørg. et al.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>293858</v>
+        <v>294011</v>
       </c>
       <c r="R20" t="n">
-        <v>6548464</v>
+        <v>6548504</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119660135</v>
+        <v>119660132</v>
       </c>
       <c r="B21" t="n">
-        <v>94410</v>
+        <v>79569</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2970,25 +2970,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2667</v>
+        <v>515</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pectenia plumbea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>293876</v>
+        <v>293858</v>
       </c>
       <c r="R21" t="n">
-        <v>6548504</v>
+        <v>6548464</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3177,10 +3177,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119660133</v>
+        <v>119660120</v>
       </c>
       <c r="B23" t="n">
-        <v>79567</v>
+        <v>90971</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3193,21 +3193,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>5321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rigidoporus corticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>293859</v>
+        <v>293865</v>
       </c>
       <c r="R23" t="n">
-        <v>6548466</v>
+        <v>6548470</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3261,23 +3261,9 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3294,7 +3280,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119660129</v>
+        <v>119660128</v>
       </c>
       <c r="B24" t="n">
         <v>74577</v>
@@ -3334,10 +3320,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>293892</v>
+        <v>293901</v>
       </c>
       <c r="R24" t="n">
-        <v>6548485</v>
+        <v>6548493</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3411,10 +3397,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119660120</v>
+        <v>119660135</v>
       </c>
       <c r="B25" t="n">
-        <v>90971</v>
+        <v>94410</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3427,21 +3413,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5321</v>
+        <v>2667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3451,10 +3437,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>293865</v>
+        <v>293876</v>
       </c>
       <c r="R25" t="n">
-        <v>6548470</v>
+        <v>6548504</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3495,9 +3481,23 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3514,10 +3514,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119660131</v>
+        <v>119660137</v>
       </c>
       <c r="B26" t="n">
-        <v>74577</v>
+        <v>94410</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3530,21 +3530,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>2667</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>293850</v>
+        <v>293882</v>
       </c>
       <c r="R26" t="n">
-        <v>6548486</v>
+        <v>6548507</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119660137</v>
+        <v>119660123</v>
       </c>
       <c r="B28" t="n">
-        <v>94410</v>
+        <v>74577</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2667</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>293882</v>
+        <v>294010</v>
       </c>
       <c r="R28" t="n">
-        <v>6548507</v>
+        <v>6548481</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3834,21 +3834,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3865,10 +3850,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119660128</v>
+        <v>119660133</v>
       </c>
       <c r="B29" t="n">
-        <v>74577</v>
+        <v>79567</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3881,21 +3866,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3905,10 +3890,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>293901</v>
+        <v>293859</v>
       </c>
       <c r="R29" t="n">
-        <v>6548493</v>
+        <v>6548466</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3954,17 +3939,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4084,10 +4069,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119660125</v>
+        <v>119660129</v>
       </c>
       <c r="B31" t="n">
-        <v>90573</v>
+        <v>74577</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4100,21 +4085,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1205</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4124,10 +4109,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>294011</v>
+        <v>293892</v>
       </c>
       <c r="R31" t="n">
-        <v>6548504</v>
+        <v>6548485</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4173,17 +4158,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4201,7 +4186,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119660123</v>
+        <v>119660131</v>
       </c>
       <c r="B32" t="n">
         <v>74577</v>
@@ -4241,10 +4226,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>294010</v>
+        <v>293850</v>
       </c>
       <c r="R32" t="n">
-        <v>6548481</v>
+        <v>6548486</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4287,6 +4272,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">

--- a/artfynd/A 32279-2024 artfynd.xlsx
+++ b/artfynd/A 32279-2024 artfynd.xlsx
@@ -2958,10 +2958,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119660132</v>
+        <v>119660131</v>
       </c>
       <c r="B21" t="n">
-        <v>79569</v>
+        <v>74577</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2970,25 +2970,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>515</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pectenia plumbea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lightf.) P.M.Jørg. et al.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>293858</v>
+        <v>293850</v>
       </c>
       <c r="R21" t="n">
-        <v>6548464</v>
+        <v>6548486</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3075,10 +3075,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119660110</v>
+        <v>119660129</v>
       </c>
       <c r="B22" t="n">
-        <v>91494</v>
+        <v>74577</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3091,21 +3091,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>293855</v>
+        <v>293892</v>
       </c>
       <c r="R22" t="n">
-        <v>6548516</v>
+        <v>6548485</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3161,6 +3161,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3177,10 +3192,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119660120</v>
+        <v>119660132</v>
       </c>
       <c r="B23" t="n">
-        <v>90971</v>
+        <v>79569</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3189,25 +3204,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5321</v>
+        <v>515</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Pectenia plumbea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3217,10 +3232,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>293865</v>
+        <v>293858</v>
       </c>
       <c r="R23" t="n">
-        <v>6548470</v>
+        <v>6548464</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3261,9 +3276,23 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3280,10 +3309,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119660128</v>
+        <v>119660120</v>
       </c>
       <c r="B24" t="n">
-        <v>74577</v>
+        <v>90971</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3296,21 +3325,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>5321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Rigidoporus corticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3320,10 +3349,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>293901</v>
+        <v>293865</v>
       </c>
       <c r="R24" t="n">
-        <v>6548493</v>
+        <v>6548470</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3364,23 +3393,9 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3397,10 +3412,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119660135</v>
+        <v>119660110</v>
       </c>
       <c r="B25" t="n">
-        <v>94410</v>
+        <v>91494</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3413,21 +3428,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3437,10 +3452,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>293876</v>
+        <v>293855</v>
       </c>
       <c r="R25" t="n">
-        <v>6548504</v>
+        <v>6548516</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3483,21 +3498,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3514,7 +3514,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119660137</v>
+        <v>119660135</v>
       </c>
       <c r="B26" t="n">
         <v>94410</v>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>293882</v>
+        <v>293876</v>
       </c>
       <c r="R26" t="n">
-        <v>6548507</v>
+        <v>6548504</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3631,7 +3631,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119660126</v>
+        <v>119660123</v>
       </c>
       <c r="B27" t="n">
         <v>74577</v>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>293933</v>
+        <v>294010</v>
       </c>
       <c r="R27" t="n">
-        <v>6548488</v>
+        <v>6548481</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3717,21 +3717,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3748,10 +3733,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119660123</v>
+        <v>119660133</v>
       </c>
       <c r="B28" t="n">
-        <v>74577</v>
+        <v>79567</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3764,21 +3749,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3788,10 +3773,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>294010</v>
+        <v>293859</v>
       </c>
       <c r="R28" t="n">
-        <v>6548481</v>
+        <v>6548466</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3834,6 +3819,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3850,10 +3850,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119660133</v>
+        <v>119660128</v>
       </c>
       <c r="B29" t="n">
-        <v>79567</v>
+        <v>74577</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3866,21 +3866,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>293859</v>
+        <v>293901</v>
       </c>
       <c r="R29" t="n">
-        <v>6548466</v>
+        <v>6548493</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3939,17 +3939,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119660134</v>
+        <v>119660137</v>
       </c>
       <c r="B30" t="n">
-        <v>90334</v>
+        <v>94410</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3983,21 +3983,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3215</v>
+        <v>2667</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>293867</v>
+        <v>293882</v>
       </c>
       <c r="R30" t="n">
-        <v>6548479</v>
+        <v>6548507</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4053,6 +4053,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4069,7 +4084,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119660129</v>
+        <v>119660126</v>
       </c>
       <c r="B31" t="n">
         <v>74577</v>
@@ -4109,10 +4124,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>293892</v>
+        <v>293933</v>
       </c>
       <c r="R31" t="n">
-        <v>6548485</v>
+        <v>6548488</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4186,10 +4201,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119660131</v>
+        <v>119660134</v>
       </c>
       <c r="B32" t="n">
-        <v>74577</v>
+        <v>90334</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4202,21 +4217,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>3215</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4226,10 +4241,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>293850</v>
+        <v>293867</v>
       </c>
       <c r="R32" t="n">
-        <v>6548486</v>
+        <v>6548479</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4272,21 +4287,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
